--- a/results/reliability_eval/Llama-3-8B_P17_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
+++ b/results/reliability_eval/Llama-3-8B_P17_sample_15_tokens_0.1_temp_first_thought_scores_08-24-4.xlsx
@@ -477,31 +477,31 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.5204210069444445</v>
+        <v>0.4034292821606254</v>
       </c>
       <c r="B2" t="n">
-        <v>0.3840185889045508</v>
+        <v>0.1643055029178701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5204210069444445</v>
+        <v>0.4034292821606254</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3840185889045508</v>
+        <v>0.1643055029178701</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4757291666666667</v>
+        <v>0.6033163265306123</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3734272503238181</v>
+        <v>0.2496208716573136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9935763888888889</v>
+        <v>0.9926261549395878</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9867143941530598</v>
+        <v>0.9669963435647669</v>
       </c>
       <c r="I2" t="n">
-        <v>0.36</v>
+        <v>0.196</v>
       </c>
     </row>
   </sheetData>
